--- a/raw/EstadoSistema.xlsx
+++ b/raw/EstadoSistema.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://pluspetrolnet-my.sharepoint.com/personal/rmanassero_pluspetrol_net/Documents/Desktop/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{3D6676DF-6B3F-4F8C-AAAB-385DFB263ECA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="1" documentId="8_{3D6676DF-6B3F-4F8C-AAAB-385DFB263ECA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4228EAC3-619D-40FB-A684-0C17AF8FD807}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{F9BC9450-2DBC-4B67-BC88-4F9A30C13590}"/>
   </bookViews>
@@ -440,7 +440,6 @@
         <v>0</v>
       </c>
       <c r="B1" s="1">
-        <f ca="1">+TODAY()</f>
         <v>46303</v>
       </c>
     </row>

--- a/raw/EstadoSistema.xlsx
+++ b/raw/EstadoSistema.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://pluspetrolnet-my.sharepoint.com/personal/rmanassero_pluspetrol_net/Documents/Desktop/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\estado-sistema-gas-rodrigo-clean\raw\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1" documentId="8_{3D6676DF-6B3F-4F8C-AAAB-385DFB263ECA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4228EAC3-619D-40FB-A684-0C17AF8FD807}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3AB20C61-2FFD-4C0F-A317-00CBFD7D0B17}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{F9BC9450-2DBC-4B67-BC88-4F9A30C13590}"/>
   </bookViews>
@@ -47,10 +47,10 @@
     <t>ESTADO SISTEMA TGN</t>
   </si>
   <si>
-    <t>NORMAL</t>
+    <t>ESTADO SISTEMA TGS</t>
   </si>
   <si>
-    <t>ESTADO SISTEMA TGS</t>
+    <t>NORMAL</t>
   </si>
 </sst>
 </file>
@@ -440,7 +440,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="1">
-        <v>46303</v>
+        <v>46304</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.35">
@@ -448,15 +448,15 @@
         <v>1</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
+        <v>2</v>
+      </c>
+      <c r="B3" s="2" t="s">
         <v>3</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>2</v>
       </c>
     </row>
   </sheetData>
